--- a/data/trans_dic/P42-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P42-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,45%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,61; 93,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,31; 98,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,74; 96,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,22; 93,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,99; 93,55</t>
+          <t>86,61; 93,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,41; 98,24</t>
+          <t>93,31; 98,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,4; 96,61</t>
+          <t>91,74; 96,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,01; 93,37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86,99; 93,55</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>93,41; 98,24</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>91,4; 96,61</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,01; 93,37</t>
+          <t>87,22; 93,59</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>90,34%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,54; 88,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,2; 96,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,32; 97,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,67; 93,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,72; 89,03</t>
+          <t>81,54; 88,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,08; 96,32</t>
+          <t>91,2; 96,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,25; 97,61</t>
+          <t>93,32; 97,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,63; 93,32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81,72; 89,03</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>91,08; 96,32</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>93,25; 97,61</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,63; 93,32</t>
+          <t>86,67; 93,06</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,02%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,83; 89,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,57; 95,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,11; 96,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79,97; 91,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,58; 89,25</t>
+          <t>77,83; 89,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,53; 95,41</t>
+          <t>88,57; 95,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,04; 96,77</t>
+          <t>89,11; 96,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,0; 90,87</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>77,58; 89,25</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>88,53; 95,41</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>89,04; 96,77</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>80,0; 90,87</t>
+          <t>79,97; 91,0</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64,31%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>89,63%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>64,31%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,18; 83,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,37; 91,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,06; 92,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,24; 88,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,87; 83,13</t>
+          <t>77,18; 83,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,37; 91,79</t>
+          <t>87,37; 91,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,83; 91,99</t>
+          <t>88,06; 92,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 88,77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76,87; 83,13</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>87,37; 91,79</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87,83; 91,99</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,75; 88,77</t>
+          <t>29,24; 88,91</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>87,91%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,29; 87,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,32; 90,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,02; 89,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,0; 91,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,95; 87,09</t>
+          <t>81,29; 87,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,42; 90,34</t>
+          <t>85,32; 90,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,03; 89,89</t>
+          <t>85,02; 89,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,13; 91,23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>80,95; 87,09</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>85,42; 90,34</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>85,03; 89,89</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>85,13; 91,23</t>
+          <t>85,0; 91,6</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78,2%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,67%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,65; 73,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,13; 81,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75,4; 80,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,52; 77,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,08; 73,31</t>
+          <t>68,65; 73,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,25; 81,34</t>
+          <t>76,13; 81,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,56; 80,59</t>
+          <t>75,4; 80,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,69; 77,58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>68,08; 73,31</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>76,25; 81,34</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>75,56; 80,59</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>69,69; 77,58</t>
+          <t>69,52; 77,65</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>78,67%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,72; 80,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,95; 88,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,03; 88,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,8; 85,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,56; 80,39</t>
+          <t>77,72; 80,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01; 88,24</t>
+          <t>85,95; 88,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,13; 88,39</t>
+          <t>86,03; 88,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,93; 85,32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>77,56; 80,39</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>86,01; 88,24</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>86,13; 88,39</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>59,93; 85,32</t>
+          <t>62,8; 85,61</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1308,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1660,22 +1343,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,20 +1362,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1737,26 +1408,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1773,10 +1424,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1791,22 +1438,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1825,26 +1472,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>438</t>
         </is>
@@ -1859,22 +1486,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275983</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303002</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1893,26 +1520,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>277514</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>275983</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>303002</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>327276</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>277514</t>
         </is>
@@ -1927,62 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>264596; 285096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>293427; 308642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>316885; 333794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>267599; 287158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>265757; 285801</t>
+          <t>264596; 285096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>293735; 308924</t>
+          <t>293427; 308642</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>315715; 333716</t>
+          <t>316885; 333794</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>266957; 286462</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>265757; 285801</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>293735; 308924</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>315715; 333716</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>266957; 286462</t>
+          <t>267599; 287158</t>
         </is>
       </c>
     </row>
@@ -1999,22 +1586,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2033,26 +1620,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>397</t>
         </is>
@@ -2067,22 +1634,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315209</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315195</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2101,26 +1668,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>249452</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>315209</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>315195</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>353348</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>249452</t>
         </is>
@@ -2135,62 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>300824; 328135</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>305161; 323152</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>344160; 359835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>239328; 256975</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>301507; 328495</t>
+          <t>300824; 328135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>304757; 322301</t>
+          <t>305161; 323152</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>343923; 359988</t>
+          <t>344160; 359835</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>239222; 257702</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>301507; 328495</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>304757; 322301</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>343923; 359988</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>239222; 257702</t>
+          <t>239328; 256975</t>
         </is>
       </c>
     </row>
@@ -2207,22 +1734,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2241,26 +1768,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
@@ -2275,22 +1782,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141052</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239910</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2309,26 +1816,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>102148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141052</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>239910</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155576</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>102148</t>
         </is>
@@ -2343,62 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>130585; 149569</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>229479; 247872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>148031; 160536</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>94961; 108057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130165; 149745</t>
+          <t>130585; 149569</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>229359; 247187</t>
+          <t>229479; 247872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>147909; 160752</t>
+          <t>148031; 160536</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94996; 107903</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>130165; 149745</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>229359; 247187</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>147909; 160752</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>94996; 107903</t>
+          <t>94961; 108057</t>
         </is>
       </c>
     </row>
@@ -2415,22 +1882,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2449,26 +1916,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>788</t>
         </is>
@@ -2483,22 +1930,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568575</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683397</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>741854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>489849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2517,26 +1964,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>489849</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>568575</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>683397</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>741854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>489849</t>
         </is>
@@ -2551,62 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>548235; 591912</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>666182; 699341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>724621; 760503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>222771; 677276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>546048; 590533</t>
+          <t>548235; 591912</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666200; 699874</t>
+          <t>666182; 699341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>722667; 756942</t>
+          <t>724621; 760503</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>203767; 676202</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>546048; 590533</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>666200; 699874</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>722667; 756942</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>203767; 676202</t>
+          <t>222771; 677276</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2030,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>451</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2657,26 +2064,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>868</t>
         </is>
@@ -2691,22 +2078,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474826</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665085</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>639538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2725,26 +2112,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>599860</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>474826</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>665085</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>639538</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>599860</t>
         </is>
@@ -2759,62 +2126,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>458253; 491828</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>644217; 681718</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>621181; 656675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>580001; 625050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>456329; 490953</t>
+          <t>458253; 491828</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>644993; 682143</t>
+          <t>644217; 681718</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>621283; 656786</t>
+          <t>621181; 656675</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>580870; 622497</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>456329; 490953</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>644993; 682143</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>621283; 656786</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>580870; 622497</t>
+          <t>580001; 625050</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2178,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>867</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>814</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2865,26 +2212,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>780</t>
         </is>
@@ -2899,22 +2226,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>884639</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>870451</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>836918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2933,26 +2260,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>454503</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>884639</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>870451</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>836918</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>454503</t>
         </is>
@@ -2967,62 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>855894; 915274</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>840694; 896358</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>806954; 861913</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>428890; 479000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>848820; 914034</t>
+          <t>855894; 915274</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>842023; 898162</t>
+          <t>840694; 896358</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>808745; 862568</t>
+          <t>806954; 861913</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>429933; 478605</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>848820; 914034</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>842023; 898162</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>808745; 862568</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>429933; 478605</t>
+          <t>428890; 479000</t>
         </is>
       </c>
     </row>
@@ -3039,22 +2326,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3073,26 +2360,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2583</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3449</t>
         </is>
@@ -3107,22 +2374,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2660283</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3077041</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3054509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2173326</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3141,26 +2408,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2173326</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2660283</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3077041</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3054509</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2173326</t>
         </is>
@@ -3175,62 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2613629; 2705541</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3034061; 3115281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3014640; 3095158</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1734975; 2365160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2608201; 2703420</t>
+          <t>2613629; 2705541</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3036310; 3114759</t>
+          <t>3034061; 3115281</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3018221; 3097426</t>
+          <t>3014640; 3095158</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1655621; 2357236</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2608201; 2703420</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>3036310; 3114759</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>3018221; 3097426</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1655621; 2357236</t>
+          <t>1734975; 2365160</t>
         </is>
       </c>
     </row>
@@ -3242,16 +2469,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P42-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P42-Clase-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,61; 93,32</t>
+          <t>86,24; 93,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,31; 98,15</t>
+          <t>93,35; 98,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,74; 96,63</t>
+          <t>92,2; 96,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,22; 93,59</t>
+          <t>86,6; 92,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,61; 93,32</t>
+          <t>86,24; 93,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,31; 98,15</t>
+          <t>93,35; 98,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,74; 96,63</t>
+          <t>92,2; 96,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,22; 93,59</t>
+          <t>86,6; 92,95</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,54; 88,94</t>
+          <t>81,49; 88,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,2; 96,58</t>
+          <t>90,89; 96,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,32; 97,57</t>
+          <t>93,06; 97,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,67; 93,06</t>
+          <t>87,06; 93,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,54; 88,94</t>
+          <t>81,49; 88,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,2; 96,58</t>
+          <t>90,89; 96,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,32; 97,57</t>
+          <t>93,06; 97,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,67; 93,06</t>
+          <t>87,06; 93,68</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,83; 89,14</t>
+          <t>77,67; 89,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,57; 95,67</t>
+          <t>88,81; 95,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,64</t>
+          <t>89,09; 96,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,97; 91,0</t>
+          <t>79,35; 90,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,83; 89,14</t>
+          <t>77,67; 89,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,57; 95,67</t>
+          <t>88,81; 95,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,64</t>
+          <t>89,09; 96,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79,97; 91,0</t>
+          <t>79,35; 90,15</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,18; 83,33</t>
+          <t>76,97; 82,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,37; 91,72</t>
+          <t>87,15; 91,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,42</t>
+          <t>87,88; 91,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 88,91</t>
+          <t>85,53; 90,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,18; 83,33</t>
+          <t>76,97; 82,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,37; 91,72</t>
+          <t>87,15; 91,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,42</t>
+          <t>87,88; 91,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 88,91</t>
+          <t>85,53; 90,16</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1061,49 +1061,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,29; 87,25</t>
+          <t>80,89; 87,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,32; 90,28</t>
+          <t>85,62; 90,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,87</t>
+          <t>85,01; 89,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,0; 91,6</t>
+          <t>81,92; 87,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,29; 87,25</t>
+          <t>80,89; 87,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,32; 90,28</t>
+          <t>85,62; 90,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,87</t>
+          <t>85,01; 89,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,0; 91,6</t>
+          <t>81,92; 87,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,65; 73,41</t>
+          <t>68,55; 73,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76,13; 81,17</t>
+          <t>76,3; 81,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,4; 80,53</t>
+          <t>75,4; 80,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,52; 77,65</t>
+          <t>69,01; 77,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,65; 73,41</t>
+          <t>68,55; 73,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,13; 81,17</t>
+          <t>76,3; 81,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,4; 80,53</t>
+          <t>75,4; 80,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,52; 77,65</t>
+          <t>69,01; 77,21</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,72; 80,45</t>
+          <t>77,7; 80,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,95; 88,25</t>
+          <t>86,06; 88,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,03; 88,33</t>
+          <t>85,98; 88,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,8; 85,61</t>
+          <t>82,31; 85,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,72; 80,45</t>
+          <t>77,7; 80,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,95; 88,25</t>
+          <t>86,06; 88,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,03; 88,33</t>
+          <t>85,98; 88,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,8; 85,61</t>
+          <t>82,31; 85,24</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277514</t>
+          <t>303164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>277514</t>
+          <t>303164</t>
         </is>
       </c>
     </row>
@@ -1534,42 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>264596; 285096</t>
+          <t>263465; 284840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>293427; 308642</t>
+          <t>293528; 308508</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>316885; 333794</t>
+          <t>318474; 334543</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267599; 287158</t>
+          <t>291229; 312589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>264596; 285096</t>
+          <t>263465; 284840</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>293427; 308642</t>
+          <t>293528; 308508</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>316885; 333794</t>
+          <t>318474; 334543</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>267599; 287158</t>
+          <t>291229; 312589</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249452</t>
+          <t>280289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>249452</t>
+          <t>280289</t>
         </is>
       </c>
     </row>
@@ -1682,42 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>300824; 328135</t>
+          <t>300657; 327577</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>305161; 323152</t>
+          <t>304131; 322072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>344160; 359835</t>
+          <t>343212; 359522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>239328; 256975</t>
+          <t>269054; 289520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>300824; 328135</t>
+          <t>300657; 327577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>305161; 323152</t>
+          <t>304131; 322072</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>344160; 359835</t>
+          <t>343212; 359522</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>239328; 256975</t>
+          <t>269054; 289520</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>112427</t>
         </is>
       </c>
     </row>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>130585; 149569</t>
+          <t>130313; 149939</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>229479; 247872</t>
+          <t>230098; 247696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148031; 160536</t>
+          <t>148003; 160835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94961; 108057</t>
+          <t>104807; 119067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130585; 149569</t>
+          <t>130313; 149939</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>229479; 247872</t>
+          <t>230098; 247696</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>148031; 160536</t>
+          <t>148003; 160835</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94961; 108057</t>
+          <t>104807; 119067</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>547497</t>
         </is>
       </c>
     </row>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>548235; 591912</t>
+          <t>546740; 586952</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666182; 699341</t>
+          <t>664498; 698837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>724621; 760503</t>
+          <t>723124; 756898</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222771; 677276</t>
+          <t>531892; 560665</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>548235; 591912</t>
+          <t>546740; 586952</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666182; 699341</t>
+          <t>664498; 698837</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>724621; 760503</t>
+          <t>723124; 756898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>222771; 677276</t>
+          <t>531892; 560665</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599860</t>
+          <t>550626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>599860</t>
+          <t>550626</t>
         </is>
       </c>
     </row>
@@ -2126,49 +2126,49 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>458253; 491828</t>
+          <t>455999; 491901</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644217; 681718</t>
+          <t>646507; 681956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>621181; 656675</t>
+          <t>621154; 657174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>580001; 625050</t>
+          <t>532183; 566128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>458253; 491828</t>
+          <t>455999; 491901</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>644217; 681718</t>
+          <t>646507; 681956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>621181; 656675</t>
+          <t>621154; 657174</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>580001; 625050</t>
+          <t>532183; 566128</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>454503</t>
+          <t>495724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>454503</t>
+          <t>495724</t>
         </is>
       </c>
     </row>
@@ -2274,42 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>855894; 915274</t>
+          <t>854616; 917978</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>840694; 896358</t>
+          <t>842536; 896818</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>806954; 861913</t>
+          <t>806961; 863187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>428890; 479000</t>
+          <t>468776; 524492</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>855894; 915274</t>
+          <t>854616; 917978</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>840694; 896358</t>
+          <t>842536; 896818</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>806954; 861913</t>
+          <t>806961; 863187</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>428890; 479000</t>
+          <t>468776; 524492</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2173326</t>
+          <t>2289727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2173326</t>
+          <t>2289727</t>
         </is>
       </c>
     </row>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2613629; 2705541</t>
+          <t>2612929; 2704967</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3034061; 3115281</t>
+          <t>3037764; 3116516</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3014640; 3095158</t>
+          <t>3012935; 3095017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1734975; 2365160</t>
+          <t>2245537; 2325439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2613629; 2705541</t>
+          <t>2612929; 2704967</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3034061; 3115281</t>
+          <t>3037764; 3116516</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3014640; 3095158</t>
+          <t>3012935; 3095017</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1734975; 2365160</t>
+          <t>2245537; 2325439</t>
         </is>
       </c>
     </row>
